--- a/data/trans_dic/P6903-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,7; 37,47</t>
+          <t>16,61; 37,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 36,51</t>
+          <t>16,54; 35,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,38; 48,84</t>
+          <t>21,8; 49,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 45,19</t>
+          <t>18,46; 43,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,78; 53,83</t>
+          <t>20,8; 52,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,02; 58,05</t>
+          <t>22,57; 55,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,21; 55,15</t>
+          <t>21,02; 54,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,73; 50,98</t>
+          <t>29,17; 51,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,06; 39,77</t>
+          <t>21,8; 39,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,41; 38,17</t>
+          <t>20,62; 38,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,6; 46,63</t>
+          <t>26,0; 46,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,69; 42,58</t>
+          <t>25,88; 43,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,0; 41,05</t>
+          <t>25,68; 40,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 34,38</t>
+          <t>15,24; 33,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,16; 45,7</t>
+          <t>22,9; 44,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,79; 48,06</t>
+          <t>27,48; 49,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 36,58</t>
+          <t>12,62; 35,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,31; 49,88</t>
+          <t>24,14; 49,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,12; 58,61</t>
+          <t>32,37; 58,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,19; 49,05</t>
+          <t>32,7; 49,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,05; 36,97</t>
+          <t>24,2; 37,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,96; 35,75</t>
+          <t>21,25; 35,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 46,18</t>
+          <t>30,01; 46,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,16; 46,35</t>
+          <t>32,3; 45,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,93; 35,57</t>
+          <t>16,62; 35,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,46; 39,74</t>
+          <t>18,59; 39,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,36; 50,51</t>
+          <t>31,98; 51,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,5; 53,51</t>
+          <t>26,54; 53,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,79; 47,31</t>
+          <t>20,65; 47,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,65; 42,15</t>
+          <t>17,11; 42,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,81; 58,07</t>
+          <t>32,77; 58,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 46,85</t>
+          <t>11,32; 46,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,63; 35,55</t>
+          <t>19,93; 35,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,7; 36,4</t>
+          <t>20,89; 36,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,44; 50,02</t>
+          <t>35,04; 50,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,16; 44,13</t>
+          <t>15,57; 44,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,18; 46,32</t>
+          <t>30,51; 46,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 29,99</t>
+          <t>11,86; 29,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,53; 54,71</t>
+          <t>33,95; 54,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,6; 40,66</t>
+          <t>21,18; 40,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,26; 43,17</t>
+          <t>22,85; 43,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,79; 51,78</t>
+          <t>25,08; 51,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,4; 49,56</t>
+          <t>24,37; 48,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,82; 57,44</t>
+          <t>39,41; 58,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,05; 42,83</t>
+          <t>29,79; 42,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,24; 35,58</t>
+          <t>20,32; 35,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,15; 48,9</t>
+          <t>32,81; 48,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,78; 46,89</t>
+          <t>32,44; 46,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,29; 36,11</t>
+          <t>27,44; 36,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,21; 28,57</t>
+          <t>19,51; 28,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,68; 44,25</t>
+          <t>33,63; 44,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,69; 40,75</t>
+          <t>28,56; 39,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,09; 37,85</t>
+          <t>24,95; 36,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,46; 41,47</t>
+          <t>28,64; 41,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,45; 48,95</t>
+          <t>34,33; 47,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,29; 45,54</t>
+          <t>28,62; 45,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,76; 35,01</t>
+          <t>27,74; 35,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,5; 32,35</t>
+          <t>24,0; 32,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,71; 44,29</t>
+          <t>35,78; 44,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,06; 40,98</t>
+          <t>30,31; 40,89</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13246; 29727</t>
+          <t>13178; 29869</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11852; 27577</t>
+          <t>12492; 26852</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12234; 26701</t>
+          <t>11921; 27089</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13503; 32185</t>
+          <t>13146; 31253</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6698; 17356</t>
+          <t>6707; 16813</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7763; 20465</t>
+          <t>7955; 19467</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6047; 16499</t>
+          <t>6289; 16166</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15712; 27879</t>
+          <t>15952; 28133</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23502; 44372</t>
+          <t>24319; 43676</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22609; 42285</t>
+          <t>22843; 42580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21653; 39448</t>
+          <t>21990; 39176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32340; 53608</t>
+          <t>32579; 54586</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37948; 59924</t>
+          <t>37489; 59528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13612; 31561</t>
+          <t>13990; 30597</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23432; 44322</t>
+          <t>22206; 42932</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30815; 53289</t>
+          <t>30463; 54513</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6680; 19311</t>
+          <t>6663; 18822</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14535; 31098</t>
+          <t>15050; 30585</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17285; 32558</t>
+          <t>17982; 32632</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31780; 48423</t>
+          <t>32280; 48478</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47806; 73483</t>
+          <t>48108; 75416</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32306; 55117</t>
+          <t>32765; 55248</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45484; 70447</t>
+          <t>45782; 71590</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67406; 97154</t>
+          <t>67699; 95754</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18619; 39103</t>
+          <t>18276; 39090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14687; 31620</t>
+          <t>14793; 31094</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34480; 55528</t>
+          <t>35162; 56441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14421; 29118</t>
+          <t>14443; 29114</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9674; 22014</t>
+          <t>9610; 22135</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8819; 22333</t>
+          <t>9066; 22468</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21889; 37595</t>
+          <t>21220; 37754</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9724; 45405</t>
+          <t>10968; 45225</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30724; 55622</t>
+          <t>31184; 55754</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27437; 48244</t>
+          <t>27680; 49019</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61900; 87375</t>
+          <t>61206; 88431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22938; 66779</t>
+          <t>23567; 67155</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41365; 63479</t>
+          <t>41816; 63841</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8766; 23210</t>
+          <t>9181; 22796</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29647; 48371</t>
+          <t>30013; 48433</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21674; 40803</t>
+          <t>21257; 40549</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20593; 38227</t>
+          <t>20232; 38469</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17171; 33190</t>
+          <t>16074; 32743</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16782; 32752</t>
+          <t>16102; 31750</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40071; 59286</t>
+          <t>40673; 60785</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67795; 96628</t>
+          <t>67212; 96541</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28646; 50342</t>
+          <t>28754; 50485</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51209; 75548</t>
+          <t>50694; 75305</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66730; 95452</t>
+          <t>66045; 95571</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>128890; 170546</t>
+          <t>129613; 170683</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62308; 92651</t>
+          <t>63279; 93865</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117870; 154859</t>
+          <t>117715; 156230</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96638; 137275</t>
+          <t>96204; 133498</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55237; 83314</t>
+          <t>54919; 81376</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61107; 89027</t>
+          <t>61476; 88549</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>76669; 105873</t>
+          <t>74264; 103788</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>99999; 160985</t>
+          <t>101182; 160700</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>192224; 242444</t>
+          <t>192104; 242897</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>132031; 174382</t>
+          <t>129351; 175264</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202214; 250839</t>
+          <t>202638; 251475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>214441; 282906</t>
+          <t>209245; 282302</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6903-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,61; 37,65</t>
+          <t>16,58; 36,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,54; 35,55</t>
+          <t>16,36; 35,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,8; 49,55</t>
+          <t>22,46; 51,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,46; 43,89</t>
+          <t>19,19; 46,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,8; 52,15</t>
+          <t>19,64; 54,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,57; 55,22</t>
+          <t>21,32; 53,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,02; 54,04</t>
+          <t>21,58; 55,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,17; 51,45</t>
+          <t>29,22; 52,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,8; 39,15</t>
+          <t>20,41; 38,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,62; 38,43</t>
+          <t>20,5; 38,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26,0; 46,31</t>
+          <t>25,73; 46,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,88; 43,36</t>
+          <t>27,59; 45,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,68; 40,78</t>
+          <t>25,72; 41,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,24; 33,33</t>
+          <t>15,0; 33,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,9; 44,27</t>
+          <t>24,93; 44,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,48; 49,17</t>
+          <t>29,47; 50,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 35,65</t>
+          <t>13,51; 36,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,14; 49,06</t>
+          <t>23,39; 49,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,37; 58,74</t>
+          <t>31,31; 57,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,7; 49,1</t>
+          <t>32,49; 48,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,2; 37,94</t>
+          <t>23,76; 37,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,25; 35,84</t>
+          <t>20,48; 36,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,01; 46,93</t>
+          <t>30,07; 46,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,3; 45,68</t>
+          <t>34,14; 47,64</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 35,55</t>
+          <t>16,69; 35,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,59; 39,08</t>
+          <t>18,04; 39,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,98; 51,34</t>
+          <t>31,75; 51,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,54; 53,5</t>
+          <t>24,38; 52,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,65; 47,57</t>
+          <t>20,08; 48,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 42,41</t>
+          <t>17,01; 42,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 58,31</t>
+          <t>33,08; 57,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,32; 46,67</t>
+          <t>33,72; 56,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,93; 35,63</t>
+          <t>20,85; 36,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,89; 36,99</t>
+          <t>20,34; 37,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,04; 50,62</t>
+          <t>35,78; 50,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 44,38</t>
+          <t>32,32; 48,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,51; 46,58</t>
+          <t>29,72; 46,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,86; 29,45</t>
+          <t>11,15; 29,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 54,78</t>
+          <t>33,87; 55,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,18; 40,41</t>
+          <t>24,4; 43,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,85; 43,44</t>
+          <t>23,42; 43,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,08; 51,08</t>
+          <t>25,58; 50,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,37; 48,05</t>
+          <t>24,3; 47,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,41; 58,89</t>
+          <t>37,41; 53,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,79; 42,79</t>
+          <t>29,56; 41,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,32; 35,68</t>
+          <t>19,87; 35,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,81; 48,74</t>
+          <t>32,41; 48,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,44; 46,95</t>
+          <t>32,72; 45,58</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,44; 36,14</t>
+          <t>27,22; 35,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,51; 28,94</t>
+          <t>19,38; 28,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,63; 44,64</t>
+          <t>33,49; 44,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,56; 39,63</t>
+          <t>30,58; 41,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,95; 36,97</t>
+          <t>25,12; 37,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,64; 41,25</t>
+          <t>27,66; 41,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,33; 47,98</t>
+          <t>34,78; 48,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,62; 45,46</t>
+          <t>37,93; 47,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,74; 35,08</t>
+          <t>27,72; 34,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,0; 32,52</t>
+          <t>24,38; 32,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35,78; 44,41</t>
+          <t>35,89; 44,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,31; 40,89</t>
+          <t>35,34; 42,83</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21484</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21528</t>
+          <t>24212</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43012</t>
+          <t>48049</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13178; 29869</t>
+          <t>13153; 29291</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12492; 26852</t>
+          <t>12356; 26966</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11921; 27089</t>
+          <t>12278; 28068</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13146; 31253</t>
+          <t>14399; 34592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6707; 16813</t>
+          <t>6331; 17438</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7955; 19467</t>
+          <t>7518; 18997</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6289; 16166</t>
+          <t>6456; 16549</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15952; 28133</t>
+          <t>17479; 31128</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24319; 43676</t>
+          <t>22772; 42850</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22843; 42580</t>
+          <t>22707; 42845</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21990; 39176</t>
+          <t>21762; 39171</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32579; 54586</t>
+          <t>37206; 61484</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41638</t>
+          <t>52672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>43627</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81587</t>
+          <t>96299</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37489; 59528</t>
+          <t>37551; 60501</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13990; 30597</t>
+          <t>13767; 31046</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22206; 42932</t>
+          <t>24175; 43437</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30463; 54513</t>
+          <t>38841; 66379</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6663; 18822</t>
+          <t>7134; 19428</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15050; 30585</t>
+          <t>14586; 31154</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17982; 32632</t>
+          <t>17396; 32056</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32280; 48478</t>
+          <t>34912; 52598</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48108; 75416</t>
+          <t>47221; 74556</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32765; 55248</t>
+          <t>31570; 55678</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45782; 71590</t>
+          <t>45872; 70522</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67699; 95754</t>
+          <t>81688; 113975</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48470</t>
+          <t>56261</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18276; 39090</t>
+          <t>18353; 38598</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14793; 31094</t>
+          <t>14351; 31140</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35162; 56441</t>
+          <t>34901; 56266</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14443; 29114</t>
+          <t>16559; 35591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9610; 22135</t>
+          <t>9346; 22553</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9066; 22468</t>
+          <t>9012; 22697</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21220; 37754</t>
+          <t>21416; 37018</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10968; 45225</t>
+          <t>23848; 39795</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31184; 55754</t>
+          <t>32627; 56764</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27680; 49019</t>
+          <t>26962; 49239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61206; 88431</t>
+          <t>62495; 88605</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23567; 67155</t>
+          <t>44807; 67735</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30827</t>
+          <t>35569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48562</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80329</t>
+          <t>84130</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41816; 63841</t>
+          <t>40735; 63532</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9181; 22796</t>
+          <t>8633; 22764</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30013; 48433</t>
+          <t>29940; 49384</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21257; 40549</t>
+          <t>26197; 46530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20232; 38469</t>
+          <t>20742; 38573</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16074; 32743</t>
+          <t>16398; 32246</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16102; 31750</t>
+          <t>16060; 31622</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40673; 60785</t>
+          <t>39893; 57054</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67212; 96541</t>
+          <t>66687; 94294</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28754; 50485</t>
+          <t>28111; 49689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50694; 75305</t>
+          <t>50068; 74610</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66045; 95571</t>
+          <t>70031; 97544</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115185</t>
+          <t>137708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>138214</t>
+          <t>147031</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>253399</t>
+          <t>284739</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>129613; 170683</t>
+          <t>128558; 169966</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>63279; 93865</t>
+          <t>62856; 92954</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>117715; 156230</t>
+          <t>117232; 155947</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96204; 133498</t>
+          <t>116852; 160285</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>54919; 81376</t>
+          <t>55287; 82728</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61476; 88549</t>
+          <t>59371; 88706</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74264; 103788</t>
+          <t>75223; 104953</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>101182; 160700</t>
+          <t>130709; 162433</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>192104; 242897</t>
+          <t>191958; 242244</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129351; 175264</t>
+          <t>131419; 174395</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202638; 251475</t>
+          <t>203259; 251646</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>209245; 282302</t>
+          <t>256828; 311246</t>
         </is>
       </c>
     </row>
